--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487735_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487735_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7212</v>
+        <v>3.6018</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2739</v>
+        <v>4.0727</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5527</v>
+        <v>-0.4709</v>
       </c>
       <c r="G2" t="n">
         <v>4.915</v>
@@ -610,13 +610,13 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4928</v>
+        <v>1.3734</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1971</v>
+        <v>0.9959</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2957</v>
+        <v>0.3774</v>
       </c>
       <c r="V2" t="n">
         <v>0.6119</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.646</v>
+        <v>2.2579</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9383</v>
+        <v>0.2667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7078</v>
+        <v>1.9912</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2585</v>
+        <v>-0.437</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0256</v>
+        <v>0.103</v>
       </c>
       <c r="I3" t="n">
-        <v>0.233</v>
+        <v>-0.54</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8839</v>
+        <v>0.7836</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7621</v>
+        <v>1.4459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1218</v>
+        <v>-0.6623</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6254</v>
+        <v>-1.2206</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7366</v>
+        <v>-1.3429</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1112</v>
+        <v>0.1223</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5821</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9403</v>
+        <v>-4.8508</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5224</v>
+        <v>2.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7472</v>
+        <v>0.6337</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4887</v>
+        <v>0.6623</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2585</v>
+        <v>-0.0286</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9418</v>
+        <v>4.0015</v>
       </c>
       <c r="W3" t="n">
-        <v>1.506</v>
+        <v>3.6716</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4477</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.739</v>
+        <v>1.7996</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3339</v>
+        <v>1.637</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0729</v>
+        <v>0.1627</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.437</v>
+        <v>0.2585</v>
       </c>
       <c r="H4" t="n">
-        <v>0.103</v>
+        <v>0.0256</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.54</v>
+        <v>0.233</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7836</v>
+        <v>0.8839</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4459</v>
+        <v>0.7621</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6623</v>
+        <v>0.1218</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2206</v>
+        <v>-0.6254</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3429</v>
+        <v>-0.7366</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1223</v>
+        <v>0.1112</v>
       </c>
       <c r="P4" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-1.9403</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-4.8508</v>
-      </c>
       <c r="R4" t="n">
-        <v>2.9105</v>
+        <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1149</v>
+        <v>1.9008</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0617</v>
+        <v>1.1874</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0532</v>
+        <v>0.7134</v>
       </c>
       <c r="V4" t="n">
-        <v>4.0015</v>
+        <v>-0.9418</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6716</v>
+        <v>1.506</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3299</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RUBIO CORCHADO</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.37</v>
+        <v>0.3844</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3506</v>
+        <v>-0.8841</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7206</v>
+        <v>1.2685</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0583</v>
+        <v>1.6209</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.5688</v>
+        <v>4.2602</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5105</v>
+        <v>-2.6393</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1217</v>
+        <v>3.0582</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.104</v>
+        <v>4.9968</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0178</v>
+        <v>-1.9386</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9366</v>
+        <v>-1.4373</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4649</v>
+        <v>-0.7366</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5283</v>
+        <v>-0.7008</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1642</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-4.8508</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1344</v>
+        <v>2.5224</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1581</v>
+        <v>0.8098</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7413</v>
+        <v>0.6264</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4168</v>
+        <v>0.1834</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.894</v>
+        <v>0.2821</v>
       </c>
       <c r="W5" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.894</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>M. RUBIO CORCHADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2246</v>
+        <v>-0.0839</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0843</v>
+        <v>-1.1504</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8597</v>
+        <v>1.0665</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6209</v>
+        <v>-2.0583</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2602</v>
+        <v>-2.5688</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.6393</v>
+        <v>0.5105</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0582</v>
+        <v>-1.1217</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9968</v>
+        <v>-1.104</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9386</v>
+        <v>-0.0178</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4373</v>
+        <v>-0.9366</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7366</v>
+        <v>-1.4649</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7008</v>
+        <v>0.5283</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3284</v>
+        <v>1.1642</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8508</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5224</v>
+        <v>2.1344</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2007</v>
+        <v>1.7042</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4262</v>
+        <v>0.9415</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2254</v>
+        <v>0.7627</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2821</v>
+        <v>-0.894</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1116</v>
+        <v>-0.393</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5612</v>
+        <v>-0.0607</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5504</v>
+        <v>-0.3323</v>
       </c>
       <c r="G7" t="n">
         <v>1.3177</v>
@@ -1000,13 +1000,13 @@
         <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4008</v>
+        <v>0.3177</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3511</v>
+        <v>0.1494</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0498</v>
+        <v>0.1683</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2821</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4135</v>
+        <v>-0.804</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3117</v>
+        <v>-0.8112</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1018</v>
+        <v>0.0073</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3467</v>
@@ -1078,13 +1078,13 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4847</v>
+        <v>0.1248</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.424</v>
+        <v>0.0765</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0608</v>
+        <v>0.0482</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5705</v>
+        <v>-1.2613</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5554</v>
+        <v>-1.3552</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0152</v>
+        <v>0.0939</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1899</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4731</v>
+        <v>0.7823</v>
       </c>
       <c r="T9" t="n">
-        <v>0.498</v>
+        <v>0.6982</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0249</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2716</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7789</v>
+        <v>-2.3249</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3523</v>
+        <v>-1.9529</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4266</v>
+        <v>-0.372</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3884</v>
@@ -1234,13 +1234,13 @@
         <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0558</v>
+        <v>0.5097</v>
       </c>
       <c r="T10" t="n">
-        <v>1.153</v>
+        <v>0.5524</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2821</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8808</v>
+        <v>-2.3713</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6874</v>
+        <v>-1.287</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1933</v>
+        <v>-1.0843</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1153</v>
@@ -1312,13 +1312,13 @@
         <v>2.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9823</v>
+        <v>1.4917</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4991</v>
+        <v>0.8995</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4832</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7776</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2336</v>
+        <v>-4.5423</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0733</v>
+        <v>-1.5728</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1603</v>
+        <v>-2.9695</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7919</v>
@@ -1390,13 +1390,13 @@
         <v>1.1642</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.576</v>
+        <v>0.1152</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3028</v>
+        <v>0.1977</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2732</v>
+        <v>-0.0824</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0597</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.737299999999999</v>
+        <v>-3.736999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.097900000000001</v>
+        <v>-3.097899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6393</v>
+        <v>-0.6388999999999996</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7846</v>
+        <v>1.784600000000001</v>
       </c>
       <c r="H13" t="n">
         <v>5.8165</v>
@@ -1468,13 +1468,13 @@
         <v>19.4033</v>
       </c>
       <c r="S13" t="n">
-        <v>9.763399999999999</v>
+        <v>9.763299999999999</v>
       </c>
       <c r="T13" t="n">
         <v>6.987200000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7762</v>
+        <v>2.7761</v>
       </c>
       <c r="V13" t="n">
         <v>-4.6134</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.142200000000001</v>
+        <v>7.3391</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3898</v>
+        <v>3.8893</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7525</v>
+        <v>3.4499</v>
       </c>
       <c r="G14" t="n">
         <v>4.5156</v>
@@ -1546,13 +1546,13 @@
         <v>4.0747</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1445</v>
+        <v>-0.6586</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3174</v>
+        <v>-0.1831</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1729</v>
+        <v>-0.4755</v>
       </c>
       <c r="V14" t="n">
         <v>0.3776</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7207</v>
+        <v>2.5538</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4997</v>
+        <v>2.1994</v>
       </c>
       <c r="F15" t="n">
-        <v>0.221</v>
+        <v>0.3544</v>
       </c>
       <c r="G15" t="n">
         <v>0.2985</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4733</v>
+        <v>-0.6401</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1222</v>
+        <v>-0.1781</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5955</v>
+        <v>-0.4621</v>
       </c>
       <c r="V15" t="n">
         <v>3.6716</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,31 +1657,31 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.716</v>
+        <v>1.5983</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8661</v>
+        <v>0.6688</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8499</v>
+        <v>0.9295</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8215</v>
+        <v>-0.7039</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5233</v>
+        <v>0.9895</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7018</v>
+        <v>-1.6934</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1441</v>
+        <v>1.2617</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1194</v>
+        <v>2.3934</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2635</v>
+        <v>-1.1317</v>
       </c>
       <c r="M16" t="n">
         <v>-1.9656</v>
@@ -1693,37 +1693,37 @@
         <v>-0.5617</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3284</v>
+        <v>3.2985</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
         <v>4.2687</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7326</v>
+        <v>-0.6665</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4385</v>
+        <v>-0.5168</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1711</v>
+        <v>-0.1497</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9418</v>
+        <v>-0.3299</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2239</v>
+        <v>0.894</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,31 +1735,31 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0705</v>
+        <v>1.4608</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1683</v>
+        <v>0.3656</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9023</v>
+        <v>1.0952</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7039</v>
+        <v>-0.8215</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9895</v>
+        <v>-1.5233</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6934</v>
+        <v>0.7018</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2617</v>
+        <v>1.1441</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3934</v>
+        <v>-0.1194</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1317</v>
+        <v>1.2635</v>
       </c>
       <c r="M17" t="n">
         <v>-1.9656</v>
@@ -1771,37 +1771,37 @@
         <v>-0.5617</v>
       </c>
       <c r="P17" t="n">
-        <v>3.2985</v>
+        <v>2.3284</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
         <v>4.2687</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1943</v>
+        <v>-0.9878</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0173</v>
+        <v>-0.062</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.177</v>
+        <v>-0.9258</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3299</v>
+        <v>0.9418</v>
       </c>
       <c r="W17" t="n">
-        <v>0.894</v>
+        <v>1.2239</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.465</v>
+        <v>0.1568</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4397</v>
+        <v>-2.5484</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9046999999999999</v>
+        <v>2.7052</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4174</v>
+        <v>-1.769</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2121</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7947</v>
+        <v>-1.6767</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2462</v>
+        <v>-0.0703</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9186</v>
+        <v>1.1782</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6724</v>
+        <v>-1.2484</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1712</v>
+        <v>-1.6987</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2935</v>
+        <v>-1.2704</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1223</v>
+        <v>-0.4282</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7164</v>
+        <v>2.5224</v>
       </c>
       <c r="Q18" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.4627</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.5967</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.5377999999999999</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.0589</v>
+      </c>
+      <c r="V18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.7164</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-1.1521</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-1.2261</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-0.6119</v>
-      </c>
       <c r="W18" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5256</v>
+        <v>-0.5561</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.149</v>
+        <v>0.2395</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6234</v>
+        <v>-0.7957</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.769</v>
+        <v>-1.4174</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-2.2121</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6767</v>
+        <v>0.7947</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0703</v>
+        <v>-0.2462</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1782</v>
+        <v>-0.9186</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2484</v>
+        <v>0.6724</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6987</v>
+        <v>-1.1712</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2704</v>
+        <v>-1.2935</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4282</v>
+        <v>0.1223</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5224</v>
+        <v>2.7164</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.4627</v>
+        <v>2.7164</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.279</v>
+        <v>-1.2433</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1384</v>
+        <v>-0.1262</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1406</v>
+        <v>-1.1171</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>M. DEL VALLE REGALADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5453</v>
+        <v>-1.1443</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0682</v>
+        <v>-0.8799</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.477</v>
+        <v>-0.2645</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6426</v>
+        <v>-0.4135</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2366</v>
+        <v>-1.6659</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.406</v>
+        <v>1.2524</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5232</v>
+        <v>2.2425</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1442</v>
+        <v>0.4284</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6673</v>
+        <v>1.8141</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1195</v>
+        <v>-2.656</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3808</v>
+        <v>-2.0943</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2614</v>
+        <v>-0.5617</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9702</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.8508</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9702</v>
+        <v>4.2687</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8728</v>
+        <v>-1.0428</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5451</v>
+        <v>-0.3895</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3277</v>
+        <v>-0.6533</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. DEL VALLE REGALADO</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7088</v>
+        <v>-1.2027</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5806</v>
+        <v>-0.9681</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1282</v>
+        <v>-0.2345</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4135</v>
+        <v>-1.6426</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6659</v>
+        <v>-1.2366</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2524</v>
+        <v>-0.406</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2425</v>
+        <v>-0.5232</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4284</v>
+        <v>0.1442</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8141</v>
+        <v>-0.6673</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.656</v>
+        <v>-1.1195</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0943</v>
+        <v>-1.3808</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5617</v>
+        <v>0.2614</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.8508</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.2687</v>
+        <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6072</v>
+        <v>-0.5302</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0902</v>
+        <v>-0.445</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.517</v>
+        <v>-0.0852</v>
       </c>
       <c r="V21" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7895</v>
+        <v>-1.7016</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5632</v>
+        <v>-1.6633</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2263</v>
+        <v>-0.0383</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0095</v>
@@ -2170,13 +2170,13 @@
         <v>2.3284</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.48</v>
+        <v>-1.3921</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.12</v>
+        <v>-0.2201</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.36</v>
+        <v>-1.172</v>
       </c>
       <c r="V22" t="n">
         <v>0.2821</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8782</v>
+        <v>-4.0995</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9752999999999999</v>
+        <v>-1.2756</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9029</v>
+        <v>-2.824</v>
       </c>
       <c r="G23" t="n">
         <v>0.1785</v>
@@ -2248,13 +2248,13 @@
         <v>1.5523</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1164</v>
+        <v>-1.3377</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1828</v>
+        <v>-0.1175</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2992</v>
+        <v>-1.2202</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6119</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.737</v>
+        <v>4.404600000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02729999999999955</v>
+        <v>0.02729999999999877</v>
       </c>
       <c r="F24" t="n">
-        <v>3.71</v>
+        <v>4.3772</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7848</v>
@@ -2326,13 +2326,13 @@
         <v>30.075</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.763199999999999</v>
+        <v>-9.095800000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-2.7761</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.987100000000001</v>
+        <v>-6.3198</v>
       </c>
       <c r="V24" t="n">
         <v>4.613399999999999</v>
